--- a/artfynd/A 49956-2024 artfynd.xlsx
+++ b/artfynd/A 49956-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126166634</v>
       </c>
       <c r="B2" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126166931</v>
       </c>
       <c r="B3" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126166814</v>
       </c>
       <c r="B4" t="n">
-        <v>58020</v>
+        <v>58021</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126166789</v>
       </c>
       <c r="B5" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126167041</v>
       </c>
       <c r="B6" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 49956-2024 artfynd.xlsx
+++ b/artfynd/A 49956-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126166634</v>
       </c>
       <c r="B2" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126166931</v>
       </c>
       <c r="B3" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126166814</v>
       </c>
       <c r="B4" t="n">
-        <v>58021</v>
+        <v>58025</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126166789</v>
       </c>
       <c r="B5" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126167041</v>
       </c>
       <c r="B6" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 49956-2024 artfynd.xlsx
+++ b/artfynd/A 49956-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126166634</v>
       </c>
       <c r="B2" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126166931</v>
       </c>
       <c r="B3" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126166814</v>
       </c>
       <c r="B4" t="n">
-        <v>58025</v>
+        <v>58027</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126166789</v>
       </c>
       <c r="B5" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126167041</v>
       </c>
       <c r="B6" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 49956-2024 artfynd.xlsx
+++ b/artfynd/A 49956-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126166634</v>
+        <v>126166584</v>
       </c>
       <c r="B2" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>484746</v>
+        <v>484718</v>
       </c>
       <c r="R2" t="n">
-        <v>6839687</v>
+        <v>6839665</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -772,14 +772,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126166931</v>
+        <v>126166634</v>
       </c>
       <c r="B3" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>484802</v>
+        <v>484746</v>
       </c>
       <c r="R3" t="n">
-        <v>6839659</v>
+        <v>6839687</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126166814</v>
+        <v>126166789</v>
       </c>
       <c r="B4" t="n">
-        <v>58027</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,13 +904,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>484774</v>
+        <v>484762</v>
       </c>
       <c r="R4" t="n">
-        <v>6839659</v>
+        <v>6839680</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -966,14 +966,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126166789</v>
+        <v>126166931</v>
       </c>
       <c r="B5" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>484762</v>
+        <v>484802</v>
       </c>
       <c r="R5" t="n">
-        <v>6839680</v>
+        <v>6839659</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1066,11 +1066,11 @@
         <v>126167041</v>
       </c>
       <c r="B6" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1157,6 +1157,103 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126166814</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Mårten-Olsasmyrtäkten, Mårten-Olsasmyrtäkten, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>484774</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6839659</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49956-2024 artfynd.xlsx
+++ b/artfynd/A 49956-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126166584</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126166634</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126166789</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126166931</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126167041</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,8 +1284,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126166814</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>